--- a/quality_assessment.xlsx
+++ b/quality_assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbere\Documents\GitHub\systematic_review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodbert-e\Documents\GitHub\systematic_review_final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C58A3C-550B-4903-A8DE-8F127301DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED01C114-D9A4-4608-B62A-BB68E49E74E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="2448" windowWidth="23232" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2921" yWindow="2921" windowWidth="19562" windowHeight="10161" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grille d'extraction " sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Papiers exclus finalement" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Grille d''extraction '!$A$1:$F$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Grille d''extraction '!$A$1:$E$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Papiers groupe de patient'!$A$1:$AV$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -36,29 +36,14 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={FCC5C233-E594-49E2-9B2B-65CF6A0CF9C2}</author>
-  </authors>
-  <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{FCC5C233-E594-49E2-9B2B-65CF6A0CF9C2}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Pas forcément facile à remplir. On peut remplir de manière automatique un champ du type "subject category" à partir du nom du journal ?</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={FCC5C233-E594-49E3-9B2B-65CF6A0CF9C2}</author>
@@ -73,73 +58,145 @@
   <commentList>
     <comment ref="J1" authorId="0" shapeId="0" xr:uid="{5FD57C97-F51C-46D9-A057-4AA8369D3530}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Pas forcément facile à remplir. On peut remplir de manière automatique un champ du type "subject category" à partir du nom du journal ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="K1" authorId="1" shapeId="0" xr:uid="{B945D3EA-A4A8-47F5-8D5D-48A30C4D44E1}">
       <text>
-        <t xml:space="preserve">[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Un même article pourra avoir plusieurs objectifs... </t>
+        </r>
       </text>
     </comment>
     <comment ref="L1" authorId="2" shapeId="0" xr:uid="{B35DAD09-41F5-4448-81BC-C96623DCB719}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Pour clarifier, vous voulez indiquer ici de quel réseau il s'agit pour qu'on voie que plusieurs papiers s'appuient sur le même ? Je suis d'accord mais il faut changer l'appellation.</t>
+        </r>
       </text>
     </comment>
     <comment ref="M1" authorId="3" shapeId="0" xr:uid="{B332BCEE-4F65-441A-8600-A1C3DC902560}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Trop vague. Je mettrais : "source de données sur les transferts de patients" (ex. données administratives, électroniques, déclaratives...) ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="S1" authorId="4" shapeId="0" xr:uid="{8E74B2E7-10FD-4A78-AE6F-410AC96A25CF}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Ajouter une colonne "nombre de sites géographiques" ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z1" authorId="5" shapeId="0" xr:uid="{66FEA422-1608-4EB5-835F-39ACAF4FB8BD}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Local aussi</t>
+        </r>
       </text>
     </comment>
     <comment ref="AB1" authorId="6" shapeId="0" xr:uid="{E792622E-595E-47AB-8F65-DA0308821D0C}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     On peut distinguer le pays des données et la nationalité du premier (ou corresponding) auteur</t>
+        </r>
       </text>
     </comment>
     <comment ref="AI1" authorId="7" shapeId="0" xr:uid="{88CDEE6C-56D8-4436-A4E9-4193A790366E}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     C'est vague, vous mettez quoi là dedans ?</t>
+        </r>
       </text>
     </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={FCC5C233-E594-49E4-9B2B-65CF6A0CF9C2}</author>
@@ -154,66 +211,138 @@
   <commentList>
     <comment ref="I1" authorId="0" shapeId="0" xr:uid="{D01E2DC2-B884-4511-B793-22601C095FE7}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Pas forcément facile à remplir. On peut remplir de manière automatique un champ du type "subject category" à partir du nom du journal ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="J1" authorId="1" shapeId="0" xr:uid="{135CF34E-8974-46E6-AF32-B9618168DFE2}">
       <text>
-        <t xml:space="preserve">[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Un même article pourra avoir plusieurs objectifs... </t>
+        </r>
       </text>
     </comment>
     <comment ref="K1" authorId="2" shapeId="0" xr:uid="{F461E993-A778-49C3-9942-B179B3C4B0D9}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Pour clarifier, vous voulez indiquer ici de quel réseau il s'agit pour qu'on voie que plusieurs papiers s'appuient sur le même ? Je suis d'accord mais il faut changer l'appellation.</t>
+        </r>
       </text>
     </comment>
     <comment ref="L1" authorId="3" shapeId="0" xr:uid="{85B11E54-6018-4305-B100-D7412B7B6C91}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Trop vague. Je mettrais : "source de données sur les transferts de patients" (ex. données administratives, électroniques, déclaratives...) ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="R1" authorId="4" shapeId="0" xr:uid="{2A1B0924-1D96-4044-9B67-3329148ACD31}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Ajouter une colonne "nombre de sites géographiques" ?</t>
+        </r>
       </text>
     </comment>
     <comment ref="X1" authorId="5" shapeId="0" xr:uid="{0C236737-CFD8-4297-8D74-8A5E220B1E17}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     Local aussi</t>
+        </r>
       </text>
     </comment>
     <comment ref="Z1" authorId="6" shapeId="0" xr:uid="{197B5513-10D0-43D7-A41C-CEDD4993E001}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     On peut distinguer le pays des données et la nationalité du premier (ou corresponding) auteur</t>
+        </r>
       </text>
     </comment>
     <comment ref="AG1" authorId="7" shapeId="0" xr:uid="{36FABA06-573D-49C0-A3F9-439B21809795}">
       <text>
-        <t>[Commentaire à thread]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Commentaire à thread]
 Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
 Commentaire :
     C'est vague, vous mettez quoi là dedans ?</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -221,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="665">
   <si>
     <t>Notes</t>
   </si>
@@ -2537,228 +2666,9 @@
     <t>3</t>
   </si>
   <si>
-    <t>1 (implication directe car l'administration a permi l'usage des données, mais pas d'autre implication)</t>
-  </si>
-  <si>
-    <t>1 (remerciements à certains stakeholders pour leurs conseils et commentaires)</t>
-  </si>
-  <si>
-    <t>Non applicable</t>
-  </si>
-  <si>
-    <t>Non applicable (pas d'échantillonnage)</t>
-  </si>
-  <si>
-    <t>1 (pas de mention des acteurs du terrain bien que les politiques régionales soient intégrées dans l'étude)</t>
-  </si>
-  <si>
-    <t>2 (bien que les décideurs ne soient pas directement impliqués dans l'étude, celle-ci est conçue pour informer les responsables de santé publique)</t>
-  </si>
-  <si>
-    <t>2 (projet examiné par une instance locale : King's college information governance committee chaired by the Caldicott Guardian ; mais pas de collaboration directe ou de co-conception)</t>
-  </si>
-  <si>
-    <t>2 (données obtenues avec l'accord de l'assureur ; donc dialogue avec les partenaires mais pas de mention de co-conception)</t>
-  </si>
-  <si>
-    <t>2 (bases présentées mais choix pas comparé à d'autres option ni justifié)</t>
-  </si>
-  <si>
-    <t>2 (remerciement de certaines insituttions mais pas de collaboration explicite)</t>
-  </si>
-  <si>
-    <t>Exclusion explicite des populations non concernées par l'étude : admission &gt; 24 hours, age &gt; 18 years</t>
-  </si>
-  <si>
-    <t>2 (remerciement des collaboratuers dans l'administration qui ont donné les données, mais pas de collaboration dans le design de l'étude)</t>
-  </si>
-  <si>
-    <t>3 (données PMSI, base complète des données de séjours de patients en France)</t>
-  </si>
-  <si>
-    <t>2 (utilisation des données administratives du PMSI mais pas d'implication de partie prenante dans le choix des analyses, ou en tout cas pas de manière explicite)0</t>
-  </si>
-  <si>
-    <t>3 (bonne justification de l'exclusion des hôpitaux psychiatriques)</t>
-  </si>
-  <si>
-    <t>2 (données obtenues via accord avec autorités sanitaires mais pas de co-construction)</t>
-  </si>
-  <si>
-    <t>2 (collaboration explicite avec Geisinger mais pas de mention de co-construction)</t>
-  </si>
-  <si>
-    <t>2 (partenariat avec NHS mais pas de rôle dans conception ou analyse)</t>
-  </si>
-  <si>
-    <t>2-3 (responsables IPAC sollicités avec un questionnaire)</t>
-  </si>
-  <si>
-    <t>2-3 (soutien explicite de l'agence régionale de santé italienne pour la collecte des données)</t>
-  </si>
-  <si>
-    <t>2-3 (collaboration avec le ministère et le rivm, pas de collaboration explicite pour analyser les données)</t>
-  </si>
-  <si>
-    <t>3 (justification de l'exclusion des hôpitaux psychiatriques et de soins primaires)</t>
-  </si>
-  <si>
-    <t>2-3 (soutien des agences publiques: RIVM, DoH)</t>
-  </si>
-  <si>
-    <t>2-3 (utilisation d'une base de données sur une courte période pour simuler des données sur une grande période, ce qui limite la compréhension des dynamiques temporelles)</t>
-  </si>
-  <si>
-    <t>2-3 (partenariat avec le ministère de la santé sans mention explicite de leur rôle dans les analyses)</t>
-  </si>
-  <si>
-    <t>2 (hétérogénéité: certains hôpitaux suréchantillonnés, d'autres sous-échantillonnés, ce qui limite la représentativité nationale)</t>
-  </si>
-  <si>
-    <t>2-3 (collaboration avec PHE+NHS mais pas de rôle explicite dans les analyses)</t>
-  </si>
-  <si>
-    <t>2 (aucune donnée réelle d'introduction ou de diffusion de pathogène)</t>
-  </si>
-  <si>
-    <t>2-3 (soutien des agences publiques, pas de mention de leur rôle dans les analyses)</t>
-  </si>
-  <si>
-    <t>2-3 (collaboration avec PHE et NIHR, pas de mention de co-construction dans les analyses)</t>
-  </si>
-  <si>
-    <t>3 (base ecxhaustive de 1 an adaptée à l'objectif de mesurer les patterns de transferts actuels entre les hôpitaux)</t>
-  </si>
-  <si>
-    <t>2 (étude orientée vers les décideurs sans collaboration explicite avec eux)</t>
-  </si>
-  <si>
-    <t>2 (accès aux données CMS mais pas d'implication explicite des décideurs)</t>
-  </si>
-  <si>
-    <t>2 (étude menée au sein d'un réseau hospitalier privé, mais pas de participation explicite des professionnels ou des décideurs aux analyses)</t>
-  </si>
-  <si>
-    <t>2 (partenariat avec agences publiques, pas de participation directe)</t>
-  </si>
-  <si>
-    <t>2-3 (résultats directement pour les décideurs mais pas de collaboration explicite)</t>
-  </si>
-  <si>
-    <t>3 (exclusion de 2 hôpitaux, justifiée)</t>
-  </si>
-  <si>
-    <t>2 (hôpitaux fournissent les données, ne semblent pas impliqués dans la conception)</t>
-  </si>
-  <si>
-    <t>2 (données obtenues via l'agence de santé publique mais pas de coconstruction avec les décideurs ou autre partie prenante)</t>
-  </si>
-  <si>
-    <t>2 (pas de mention de la participation d'acteurs)</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3 (entretiens avec directeurs d'hôpitaux pour connaître leur avis)</t>
-  </si>
-  <si>
-    <t>2 '(pas d'indication sur la collaboration avec les directeurs d'hôpitaux ou autre, bien que ce soit le même réseau que Lomi_2012)</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>2 (entretiens avec des directeurs d'hôpotaux pour valider les données de flux de patients)</t>
-  </si>
-  <si>
-    <t>1-2 (pas de mention d'entretiens mais les autres articles avaient fait des entretiens avec des directeurs d'hôpotaux pour valider les données de flux de patients)</t>
-  </si>
-  <si>
-    <t>1-2 (soutien de l'agence de santé publique pour avoir les données)</t>
-  </si>
-  <si>
-    <t>1-2 (aucune mention des stakeholders sauf soutien ATIH pour données)</t>
-  </si>
-  <si>
-    <t>1-2 (pas de mention des stakeholders à part pour avoir les données)</t>
-  </si>
-  <si>
-    <t>1-2 (collaboration avec ministère de la santé pour données mais pas de co-conception)</t>
-  </si>
-  <si>
-    <t>3 (participation des autorités de santé pour décider de certains seuils)</t>
-  </si>
-  <si>
-    <t>1-2 (collaboration avec CDC pour données)</t>
-  </si>
-  <si>
-    <t>1-2 (financement public mais pas de collaboration explicite pour les analyses)</t>
-  </si>
-  <si>
-    <t>2 (soutien des autorités sanitaires)</t>
-  </si>
-  <si>
-    <t>2-3 (soutien des autorités sanitaires)</t>
-  </si>
-  <si>
-    <t>2-3 (soutien et conseils d'une personne pour l'accès et l'utilisation des données)</t>
-  </si>
-  <si>
-    <t>1-2 (collaboration d'une institution de santé publique pour l'accès aux données)</t>
-  </si>
-  <si>
-    <t>1-2 (collaboration assureur pour accès aux données)</t>
-  </si>
-  <si>
-    <t>1-Theoretical or conceptual underpinning to the research</t>
-  </si>
-  <si>
-    <t>2-Statement of research aims</t>
-  </si>
-  <si>
-    <t>3-Clear description of research setting and target population</t>
-  </si>
-  <si>
-    <t>4-The study design is appropriate to address the stated research aims</t>
-  </si>
-  <si>
-    <t>5-Appropriate sampling to address the research aims</t>
-  </si>
-  <si>
-    <t>6-Rationale for choice of data collection tools</t>
-  </si>
-  <si>
-    <t>7-The format and content of data collection tool is appropriate to address the stated research aims</t>
-  </si>
-  <si>
     <t>8-Description of data collection procedure</t>
   </si>
   <si>
-    <t>9-Recruitment data provided</t>
-  </si>
-  <si>
-    <t>10-Justification of analytic method selected</t>
-  </si>
-  <si>
-    <t>11-The method of analysis was appropriate to answer the research aims</t>
-  </si>
-  <si>
-    <t>12-Evidence that the research stakeholders have been considered in research design or conduct</t>
-  </si>
-  <si>
-    <t>13-Strengths and limitations critically discussed</t>
-  </si>
-  <si>
-    <t>0 (aucune indication de consultation avec des parties prenantes)</t>
-  </si>
-  <si>
-    <t>0 (aucune mention d'implication de stakeholders)</t>
-  </si>
-  <si>
-    <t>0 (aucune mention des stakeholders)</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -2771,261 +2681,6 @@
     <t>1-</t>
   </si>
   <si>
-    <t>2-3 (data-use agreement with CMS)</t>
-  </si>
-  <si>
-    <t>2-3 (implication des autorités sanitaires pour nettoyer, utiliser jeux de données)</t>
-  </si>
-  <si>
-    <t>2-3 (entretien avec une experte des EMS, participation à l'interprétation des résultats)</t>
-  </si>
-  <si>
-    <t>brouillon-12</t>
-  </si>
-  <si>
-    <t>2-3 (they only include acute care hospitals to study hospital partnerships in their region)</t>
-  </si>
-  <si>
-    <t>2 (in this article they did not really describe OC hospitals)</t>
-  </si>
-  <si>
-    <t>3 (included LTAC to study pathogen transmission)</t>
-  </si>
-  <si>
-    <t>1-2 (only 2 hospital sites to describe hospital activity)</t>
-  </si>
-  <si>
-    <t>1 (no info on type of facilities, no description of facilities, no info on inclusion-exclusion of patients)</t>
-  </si>
-  <si>
-    <t>2 (they describe what they do but not why)</t>
-  </si>
-  <si>
-    <t>2-3 (they do not say if they include every patient or no)</t>
-  </si>
-  <si>
-    <t>1 (in this article no info on type of hospital, patientsd included excluded etc.)</t>
-  </si>
-  <si>
-    <t>2 (sans info sur le research setting difficile de savoir s'il est approprié)</t>
-  </si>
-  <si>
-    <t>3 (PMSI to make clsuters of French hospitalsd, very appropriate)</t>
-  </si>
-  <si>
-    <t>3 (clear description of research setting)</t>
-  </si>
-  <si>
-    <t>1 (the description of their aims is very vague)</t>
-  </si>
-  <si>
-    <t>2-3 (their aim was not precise)</t>
-  </si>
-  <si>
-    <t>2 (car la description n'était pas très précise)</t>
-  </si>
-  <si>
-    <t>1-2 (description du réseau d'hôpitaux pas très précise)</t>
-  </si>
-  <si>
-    <t>3 (data from multiple states for multiple years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (voire 0, pratiquement aucune description des hôpitaux de OC, California) </t>
-  </si>
-  <si>
-    <t>2 (difficile à dire sans description)</t>
-  </si>
-  <si>
-    <t>3 (description longue et complète des hôpitaux visés)</t>
-  </si>
-  <si>
-    <t>2 (ils expliquent ce qu'ils font, mais pas vraiment d'explication claire de leur objectif dans l'intro)</t>
-  </si>
-  <si>
-    <t>2 (ou 3, explication de l'application de network analysis à l'analyse des flux hospitaliers mais pas de discussion sur les réseaux déjà faits ou autre)</t>
-  </si>
-  <si>
-    <t>2 (voire 1 peut-être?)</t>
-  </si>
-  <si>
-    <t>1 (pas de contexte sur les réseaux de soin)</t>
-  </si>
-  <si>
-    <t>0-1 (ils parlent en quelques mots des patient transfers et ne citent qu'une étude)</t>
-  </si>
-  <si>
-    <t>0-1 (pas d'intro sur transferts de patients, réseaux, etc.)</t>
-  </si>
-  <si>
-    <t>0 (aucune justification du choix des données administratives)</t>
-  </si>
-  <si>
-    <t>1 (pas vraiment de justification explicite)</t>
-  </si>
-  <si>
-    <t>1 (source précisée mais pas d'explication sur leur adéquation)</t>
-  </si>
-  <si>
-    <t>1 (données assureur, utilisées car disponubiles mais pas d'autres jusitfications de leur choix)</t>
-  </si>
-  <si>
-    <t>1 (données assureur, utilisées car disponubiles mais pas d'autres jusitfications sur leur pertinence)</t>
-  </si>
-  <si>
-    <t>1 (données bien documentées mais pas de justification sur leur pertinence plutôt qu'autre chose)</t>
-  </si>
-  <si>
-    <t>1 (pas de justification même si bonne description des données)</t>
-  </si>
-  <si>
-    <t>0 (pas de justification ni de description de la base de données)</t>
-  </si>
-  <si>
-    <t>1 (description précise des bases de données en Angleterre et aux Pays bas, mais pas de justifiation de la limitation à un an)</t>
-  </si>
-  <si>
-    <t>1 (pas de justification du choix de ces 2 hôpitaux ni de la pertinence de ces bases de données plutôt que d'autres)</t>
-  </si>
-  <si>
-    <t>1-2 (pas de justif)</t>
-  </si>
-  <si>
-    <t>1 (pas de justif)</t>
-  </si>
-  <si>
-    <t>3 (paragraphe de justif)</t>
-  </si>
-  <si>
-    <t>3 (données PMSI, choisie car base complète des données de séjours de patients en France)</t>
-  </si>
-  <si>
-    <t>3 (justif car PMSI base de données exhaustive en France)</t>
-  </si>
-  <si>
-    <t>1 (l'article mentionne l'utilisation de ces bases de données mais pas vraiment de justification de l'intérêt de celles-ci)</t>
-  </si>
-  <si>
-    <t>1 (trop courte durée des données de transferts de patients)</t>
-  </si>
-  <si>
-    <t>2 (voire 1? certaines données viennent de survey)</t>
-  </si>
-  <si>
-    <t>2 (données sur un seul état)</t>
-  </si>
-  <si>
-    <t>3 (bdd exhaustive)</t>
-  </si>
-  <si>
-    <t>3 (bdd exhaustive sur pls années)</t>
-  </si>
-  <si>
-    <t>3 (bdd exhaustive de Sicile sur pls années)</t>
-  </si>
-  <si>
-    <t>3 (bdd de 2 hôpitaux, vérifiée institutionnellement)</t>
-  </si>
-  <si>
-    <t>2 (bdd ne couvre que patients couverts par AOK)</t>
-  </si>
-  <si>
-    <t>2 (données AOK partielles, environ 50% des patients)</t>
-  </si>
-  <si>
-    <t>3 (données quasi exhaustives sur 2 états)</t>
-  </si>
-  <si>
-    <t>2 (données exhaustives 1 an, une seule région)</t>
-  </si>
-  <si>
-    <t>2 (Medicare, pas tous les patients)</t>
-  </si>
-  <si>
-    <t>2 (un seul hôpital)</t>
-  </si>
-  <si>
-    <t>2 (une seule région)</t>
-  </si>
-  <si>
-    <t>2 (une partie d'un état, limité car fournisseur de soins de santé)</t>
-  </si>
-  <si>
-    <t>3 (administrative database, all of England)</t>
-  </si>
-  <si>
-    <t>3 (exhaustive administrative database)</t>
-  </si>
-  <si>
-    <t>3 (données exhaustives, plusieurs états)</t>
-  </si>
-  <si>
-    <t>3 (PMSI, bdd exhaustive en France)</t>
-  </si>
-  <si>
-    <t>2 (données exhaustives, une seule région)</t>
-  </si>
-  <si>
-    <t>2 (1 hospital)</t>
-  </si>
-  <si>
-    <t>2 (données exhaustives, mais un seul état)</t>
-  </si>
-  <si>
-    <t>3 (données exhaustives, plusieurs états, plusieurs années)</t>
-  </si>
-  <si>
-    <t>3 (5 hospitals)</t>
-  </si>
-  <si>
-    <t>2 (données exhaustives, mais juste Singapour)</t>
-  </si>
-  <si>
-    <t>3 (données systématiques Scotland)</t>
-  </si>
-  <si>
-    <t>3 (données exhaustives pays)</t>
-  </si>
-  <si>
-    <t>2 (AOK données partielles)</t>
-  </si>
-  <si>
-    <t>0 (je n'ai vu aucun commentaire sur les forces/faiblesses des analyses stats)</t>
-  </si>
-  <si>
-    <t>3 (they identify covariates based on previous studies + discuss in a paragraph the strengths and limitations)</t>
-  </si>
-  <si>
-    <t>2 (parameters chosen from previous studies, un peu discutés)</t>
-  </si>
-  <si>
-    <t>3 (voire 2, très bonne description, justficiation un peu courte)</t>
-  </si>
-  <si>
-    <t>1 (they choose a model based on references)</t>
-  </si>
-  <si>
-    <t>2 (they discuss the model in the conclusion)</t>
-  </si>
-  <si>
-    <t>2 (voire 1, descirption mais pas de justification</t>
-  </si>
-  <si>
-    <t>2 (justif dans méthodes mais pas discuté)</t>
-  </si>
-  <si>
-    <t>2 (s'appuient sur la littérature + discutent la mesure qu'ils ont introduite)</t>
-  </si>
-  <si>
-    <t>2 (voire 1, peu de justif hormis les rèfs)</t>
-  </si>
-  <si>
-    <t>1 (voire 0)</t>
-  </si>
-  <si>
-    <t>1 (voire 2)</t>
-  </si>
-  <si>
     <t>Donvito_2025</t>
   </si>
   <si>
@@ -3086,22 +2741,43 @@
     <t>Health Services Research</t>
   </si>
   <si>
-    <t>3 (voire 2)</t>
-  </si>
-  <si>
     <t>Asl_2025b</t>
   </si>
   <si>
     <t>Asl_2025a</t>
   </si>
   <si>
-    <t>2 (données exhaustives, un seul hôpital)</t>
-  </si>
-  <si>
-    <t>3 (données exhaustives CMS)</t>
-  </si>
-  <si>
-    <t>3 (données exhaustives)</t>
+    <t>2-Aims</t>
+  </si>
+  <si>
+    <t>4-Research setting adequacy</t>
+  </si>
+  <si>
+    <t>9-Analytic method adequacy</t>
+  </si>
+  <si>
+    <t>10-Stakeholder input</t>
+  </si>
+  <si>
+    <t>11-Strengths and limits</t>
+  </si>
+  <si>
+    <t>8-Analytic method rationale</t>
+  </si>
+  <si>
+    <t>7-Recruitment data provided</t>
+  </si>
+  <si>
+    <t>5-Data choice rationale</t>
+  </si>
+  <si>
+    <t>6-Data adequacy</t>
+  </si>
+  <si>
+    <t>1-Conceptual basis2</t>
+  </si>
+  <si>
+    <t>3-Research setting and target population description2</t>
   </si>
 </sst>
 </file>
@@ -3321,7 +2997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3382,9 +3058,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3394,12 +3067,26 @@
     <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -3457,7 +3144,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3477,7 +3164,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3497,7 +3184,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3517,11 +3204,11 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
-        <patternFill patternType="none">
+        <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor auto="1"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3569,7 +3256,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3589,7 +3276,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3609,13 +3296,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3635,51 +3316,11 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3755,31 +3396,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4BDE59E-1FAB-466E-BADB-B6A4C84C89BC}" name="Tableau1" displayName="Tableau1" ref="A1:S80" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16">
-  <autoFilter ref="A1:S80" xr:uid="{B4BDE59E-1FAB-466E-BADB-B6A4C84C89BC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4BDE59E-1FAB-466E-BADB-B6A4C84C89BC}" name="Tableau1" displayName="Tableau1" ref="A1:Q80" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14">
+  <autoFilter ref="A1:Q80" xr:uid="{B4BDE59E-1FAB-466E-BADB-B6A4C84C89BC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q74">
     <sortCondition ref="A1:A74"/>
   </sortState>
-  <tableColumns count="19">
+  <tableColumns count="17">
     <tableColumn id="4" xr3:uid="{65A3361D-3A15-40FA-91DC-18620E5FD9AC}" name="author_year"/>
-    <tableColumn id="5" xr3:uid="{2058D7F5-6509-4F07-A073-C172F249B5BD}" name="title" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{2058D7F5-6509-4F07-A073-C172F249B5BD}" name="title" dataDxfId="12"/>
     <tableColumn id="6" xr3:uid="{35ADF358-A5D2-49DB-955D-C8306A1B3690}" name="authors"/>
     <tableColumn id="11" xr3:uid="{E05220F3-D988-41F2-83F2-00CD770CD16A}" name="year_publi"/>
     <tableColumn id="12" xr3:uid="{14103147-0C7D-40F0-B2A8-0F338A4CA2CB}" name="journal"/>
-    <tableColumn id="13" xr3:uid="{972C14FE-B208-453D-B6C1-5A01B14F26E3}" name="1-Theoretical or conceptual underpinning to the research" dataDxfId="13"/>
-    <tableColumn id="1" xr3:uid="{6EE70FC6-4663-42AC-95A3-F2715BF69928}" name="2-Statement of research aims" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{37893F72-4E02-486B-9594-52FED0243266}" name="3-Clear description of research setting and target population" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{BFEBBB9F-F5F1-402B-8EE7-DBFFE5C788D0}" name="4-The study design is appropriate to address the stated research aims" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{8648B6AC-96EE-407E-A695-639C1E4C9D01}" name="5-Appropriate sampling to address the research aims" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{911AE30C-7DC1-4749-A447-E08E1A3B55CD}" name="6-Rationale for choice of data collection tools" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{0C6E8544-CE5E-43E8-9509-633C98D96938}" name="7-The format and content of data collection tool is appropriate to address the stated research aims" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{AF780E14-BF1D-4875-A631-A61821106B9C}" name="1-Conceptual basis2" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{07EA1E7B-F017-4588-8618-AF55D4D5CDAA}" name="2-Aims" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{7768FDA1-2A76-4D3D-B907-5F322D91F376}" name="3-Research setting and target population description2" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{04D87778-43E1-4580-BD83-5CCA5AADC713}" name="4-Research setting adequacy" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{6251A80B-9FA9-49E1-9529-D66CAF3A4B1A}" name="5-Data choice rationale" dataDxfId="7"/>
     <tableColumn id="10" xr3:uid="{A63FD620-3546-4C47-8F4F-92431746C476}" name="8-Description of data collection procedure" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{9A71DC20-7692-40AA-BF4B-B28A0FAAE746}" name="9-Recruitment data provided" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{47289CD0-5276-4335-8EBC-E063F6225A4B}" name="10-Justification of analytic method selected" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{93EC0195-396A-4E98-84E3-7306A1D68DD2}" name="11-The method of analysis was appropriate to answer the research aims" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{DDC57EB9-5028-448A-8CC7-3D95A31CD3B4}" name="12-Evidence that the research stakeholders have been considered in research design or conduct" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{0A14D541-206A-40B3-8242-E9ECDC997816}" name="13-Strengths and limitations critically discussed" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{E37A77D3-377E-447D-AE64-3A9EB1439F5E}" name="brouillon-12" dataDxfId="0"/>
+    <tableColumn id="22" xr3:uid="{F681B52C-9F47-4538-A750-33D83A25A309}" name="6-Data adequacy" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{A881DB85-DD68-4CEC-870E-677A037EFE26}" name="7-Recruitment data provided" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{1CFAEDC1-1EFC-4ACC-A22B-44C865B70E25}" name="8-Analytic method rationale" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{B4FF67BB-AC61-45E2-B231-7AD813EABD53}" name="9-Analytic method adequacy" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{DDC57EB9-5028-448A-8CC7-3D95A31CD3B4}" name="10-Stakeholder input" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{0A14D541-206A-40B3-8242-E9ECDC997816}" name="11-Strengths and limits" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4113,32 +3752,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AR80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.875" defaultRowHeight="14.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
-    <col min="2" max="2" width="67.33203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="177.77734375" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="67.375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="177.75" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="40.33203125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="36.5546875" customWidth="1"/>
-    <col min="8" max="8" width="35.33203125" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" customWidth="1"/>
-    <col min="10" max="10" width="25.5546875" style="24" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" customWidth="1"/>
-    <col min="12" max="12" width="40.77734375" customWidth="1"/>
-    <col min="13" max="13" width="29.77734375" style="24" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="28.88671875" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" customWidth="1"/>
-    <col min="16" max="16" width="32.5546875" customWidth="1"/>
-    <col min="17" max="17" width="42.6640625" customWidth="1"/>
-    <col min="18" max="18" width="25.6640625" customWidth="1"/>
-    <col min="19" max="19" width="43.21875" customWidth="1"/>
+    <col min="6" max="6" width="25.5" style="31" customWidth="1"/>
+    <col min="7" max="7" width="36.5" style="34" customWidth="1"/>
+    <col min="8" max="8" width="35.375" style="34" customWidth="1"/>
+    <col min="9" max="9" width="30.75" style="34" customWidth="1"/>
+    <col min="10" max="10" width="29.375" style="34" customWidth="1"/>
+    <col min="11" max="11" width="29.75" style="24" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="29.75" style="36" customWidth="1"/>
+    <col min="13" max="13" width="28.875" style="34" customWidth="1"/>
+    <col min="14" max="14" width="23.375" style="34" customWidth="1"/>
+    <col min="15" max="15" width="32.5" style="34" customWidth="1"/>
+    <col min="16" max="16" width="42.625" customWidth="1"/>
+    <col min="17" max="17" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="6" customFormat="1" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" s="6" customFormat="1" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>609</v>
       </c>
@@ -4154,50 +3791,44 @@
       <c r="E1" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>686</v>
+      <c r="F1" s="32" t="s">
+        <v>663</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>654</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>688</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>689</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>690</v>
+        <v>664</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>655</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>661</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>627</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>691</v>
-      </c>
-      <c r="M1" s="30" t="s">
-        <v>692</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>694</v>
+        <v>662</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>660</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>659</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>656</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>695</v>
+        <v>657</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>696</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="2" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>45</v>
       </c>
@@ -4213,50 +3844,44 @@
       <c r="E2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G2" s="29">
-        <v>3</v>
-      </c>
-      <c r="H2" s="29">
-        <v>3</v>
-      </c>
-      <c r="I2" s="29">
-        <v>3</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>630</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>734</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="M2" s="31" t="s">
+      <c r="F2" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="K2" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N2" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O2" s="29" t="s">
-        <v>778</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S2" s="29" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" spans="1:46" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L2" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O2" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" s="1" customFormat="1" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>597</v>
       </c>
@@ -4272,48 +3897,44 @@
       <c r="E3" t="s">
         <v>455</v>
       </c>
-      <c r="F3" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G3" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>709</v>
-      </c>
-      <c r="J3" s="31" t="s">
+      <c r="F3" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J3" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K3" s="29" t="s">
-        <v>734</v>
-      </c>
-      <c r="L3" s="29" t="s">
-        <v>754</v>
-      </c>
-      <c r="M3" s="31" t="s">
+      <c r="K3" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N3" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O3" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P3" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q3" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S3" s="29" t="s">
-        <v>628</v>
-      </c>
+      <c r="L3" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O3" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="R3"/>
+      <c r="S3"/>
       <c r="T3"/>
       <c r="U3"/>
       <c r="V3"/>
@@ -4339,10 +3960,8 @@
       <c r="AP3"/>
       <c r="AQ3"/>
       <c r="AR3"/>
-      <c r="AS3"/>
-      <c r="AT3"/>
-    </row>
-    <row r="4" spans="1:46" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:44" s="1" customFormat="1" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -4358,48 +3977,44 @@
       <c r="E4" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K4" s="29" t="s">
-        <v>735</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>755</v>
-      </c>
-      <c r="M4" s="31" t="s">
+      <c r="F4" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K4" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N4" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>779</v>
-      </c>
-      <c r="P4" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q4" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S4" s="29" t="s">
-        <v>631</v>
-      </c>
+      <c r="L4" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O4" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P4" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="R4"/>
+      <c r="S4"/>
       <c r="T4"/>
       <c r="U4"/>
       <c r="V4"/>
@@ -4425,10 +4040,8 @@
       <c r="AP4"/>
       <c r="AQ4"/>
       <c r="AR4"/>
-      <c r="AS4"/>
-      <c r="AT4"/>
-    </row>
-    <row r="5" spans="1:46" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:44" s="1" customFormat="1" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>594</v>
       </c>
@@ -4444,48 +4057,44 @@
       <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>710</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>711</v>
-      </c>
-      <c r="J5" s="31" t="s">
+      <c r="F5" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M5" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K5" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O5" s="29" t="s">
-        <v>780</v>
-      </c>
-      <c r="P5" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R5" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>632</v>
-      </c>
+      <c r="N5" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O5" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="R5"/>
+      <c r="S5"/>
       <c r="T5"/>
       <c r="U5"/>
       <c r="V5"/>
@@ -4511,10 +4120,8 @@
       <c r="AP5"/>
       <c r="AQ5"/>
       <c r="AR5"/>
-      <c r="AS5"/>
-      <c r="AT5"/>
-    </row>
-    <row r="6" spans="1:46" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:44" s="1" customFormat="1" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>70</v>
       </c>
@@ -4530,48 +4137,44 @@
       <c r="E6" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>712</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>736</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>756</v>
-      </c>
-      <c r="M6" s="31" t="s">
+      <c r="F6" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K6" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N6" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O6" s="29" t="s">
-        <v>781</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q6" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R6" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S6" s="29" t="s">
-        <v>633</v>
-      </c>
+      <c r="L6" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M6" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N6" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O6" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="R6"/>
+      <c r="S6"/>
       <c r="T6"/>
       <c r="U6"/>
       <c r="V6"/>
@@ -4597,10 +4200,8 @@
       <c r="AP6"/>
       <c r="AQ6"/>
       <c r="AR6"/>
-      <c r="AS6"/>
-      <c r="AT6"/>
-    </row>
-    <row r="7" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:44" s="1" customFormat="1" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>553</v>
       </c>
@@ -4616,48 +4217,44 @@
       <c r="E7" t="s">
         <v>587</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>667</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>713</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="J7" s="31" t="s">
+      <c r="F7" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M7" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O7" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P7" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q7" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="K7" s="29" t="s">
-        <v>737</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>757</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O7" s="29" t="s">
-        <v>782</v>
-      </c>
-      <c r="P7" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q7" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S7" s="29" t="s">
-        <v>634</v>
-      </c>
+      <c r="R7"/>
+      <c r="S7"/>
       <c r="T7"/>
       <c r="U7"/>
       <c r="V7"/>
@@ -4683,10 +4280,8 @@
       <c r="AP7"/>
       <c r="AQ7"/>
       <c r="AR7"/>
-      <c r="AS7"/>
-      <c r="AT7"/>
-    </row>
-    <row r="8" spans="1:46" s="1" customFormat="1" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:44" s="1" customFormat="1" ht="103.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>556</v>
       </c>
@@ -4702,48 +4297,44 @@
       <c r="E8" t="s">
         <v>559</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>667</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>714</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>713</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="J8" s="31" t="s">
+      <c r="F8" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M8" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q8" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="K8" s="29" t="s">
-        <v>738</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>758</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O8" s="29" t="s">
-        <v>783</v>
-      </c>
-      <c r="P8" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q8" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R8" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S8" s="29" t="s">
-        <v>634</v>
-      </c>
+      <c r="R8"/>
+      <c r="S8"/>
       <c r="T8"/>
       <c r="U8"/>
       <c r="V8"/>
@@ -4769,10 +4360,8 @@
       <c r="AP8"/>
       <c r="AQ8"/>
       <c r="AR8"/>
-      <c r="AS8"/>
-      <c r="AT8"/>
-    </row>
-    <row r="9" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -4788,50 +4377,44 @@
       <c r="E9" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>759</v>
-      </c>
-      <c r="M9" s="31" t="s">
+      <c r="F9" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N9" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>784</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q9" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R9" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S9" s="29" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="L9" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M9" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>456</v>
       </c>
@@ -4847,50 +4430,44 @@
       <c r="E10" t="s">
         <v>459</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>714</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I10" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>760</v>
-      </c>
-      <c r="M10" s="31" t="s">
+      <c r="F10" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K10" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N10" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O10" s="29" t="s">
-        <v>785</v>
-      </c>
-      <c r="P10" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R10" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S10" s="29" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="11" spans="1:46" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L10" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M10" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O10" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P10" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>424</v>
       </c>
@@ -4906,50 +4483,44 @@
       <c r="E11" t="s">
         <v>365</v>
       </c>
-      <c r="F11" s="28" t="s">
-        <v>730</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J11" s="31" t="s">
+      <c r="F11" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M11" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K11" s="29" t="s">
-        <v>739</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>761</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O11" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P11" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R11" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S11" s="29" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="12" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N11" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P11" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q11" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>98</v>
       </c>
@@ -4965,50 +4536,44 @@
       <c r="E12" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>730</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>637</v>
-      </c>
-      <c r="K12" s="29" t="s">
-        <v>740</v>
-      </c>
-      <c r="L12" s="29" t="s">
-        <v>762</v>
-      </c>
-      <c r="M12" s="31" t="s">
+      <c r="F12" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K12" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N12" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O12" s="29" t="s">
-        <v>786</v>
-      </c>
-      <c r="P12" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q12" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R12" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S12" s="29" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="13" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L12" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M12" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O12" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P12" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>105</v>
       </c>
@@ -5024,50 +4589,44 @@
       <c r="E13" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>715</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J13" s="31" t="s">
+      <c r="F13" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M13" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K13" s="29" t="s">
-        <v>740</v>
-      </c>
-      <c r="L13" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M13" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N13" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O13" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R13" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S13" s="29" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="14" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N13" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P13" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q13" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="14" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>110</v>
       </c>
@@ -5083,50 +4642,44 @@
       <c r="E14" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="28" t="s">
-        <v>731</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>716</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>717</v>
-      </c>
-      <c r="J14" s="31" t="s">
+      <c r="F14" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J14" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K14" s="29" t="s">
-        <v>741</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M14" s="31" t="s">
+      <c r="K14" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N14" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O14" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P14" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q14" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R14" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S14" s="29" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="15" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L14" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M14" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>460</v>
       </c>
@@ -5142,50 +4695,44 @@
       <c r="E15" t="s">
         <v>599</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>719</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>718</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>747</v>
-      </c>
-      <c r="L15" s="29" t="s">
-        <v>639</v>
-      </c>
-      <c r="M15" s="31" t="s">
+      <c r="F15" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K15" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N15" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O15" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P15" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q15" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R15" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S15" s="29" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="16" spans="1:46" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L15" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O15" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P15" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>114</v>
       </c>
@@ -5201,50 +4748,44 @@
       <c r="E16" t="s">
         <v>600</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>641</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>742</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>753</v>
-      </c>
-      <c r="M16" s="31" t="s">
+      <c r="F16" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N16" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O16" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P16" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q16" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R16" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S16" s="29" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L16" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O16" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P16" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q16" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -5260,50 +4801,44 @@
       <c r="E17" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>720</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I17" s="29" t="s">
-        <v>721</v>
-      </c>
-      <c r="J17" s="31" t="s">
+      <c r="F17" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M17" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K17" s="29" t="s">
-        <v>743</v>
-      </c>
-      <c r="L17" s="29" t="s">
-        <v>764</v>
-      </c>
-      <c r="M17" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N17" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O17" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P17" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q17" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R17" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S17" s="29" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O17" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P17" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q17" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>463</v>
       </c>
@@ -5319,50 +4854,44 @@
       <c r="E18" t="s">
         <v>465</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I18" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J18" s="31" t="s">
+      <c r="F18" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L18" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M18" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K18" s="29" t="s">
-        <v>744</v>
-      </c>
-      <c r="L18" s="29" t="s">
-        <v>765</v>
-      </c>
-      <c r="M18" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N18" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P18" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q18" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R18" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S18" s="29" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N18" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O18" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P18" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q18" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -5378,50 +4907,44 @@
       <c r="E19" t="s">
         <v>125</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>723</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>722</v>
-      </c>
-      <c r="J19" s="31" t="s">
+      <c r="F19" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K19" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="M19" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K19" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L19" s="29" t="s">
-        <v>766</v>
-      </c>
-      <c r="M19" s="29" t="s">
-        <v>624</v>
-      </c>
-      <c r="N19" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O19" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P19" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q19" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="R19" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S19" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N19" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O19" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P19" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q19" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>412</v>
       </c>
@@ -5437,50 +4960,44 @@
       <c r="E20" t="s">
         <v>599</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I20" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J20" s="31" t="s">
+      <c r="F20" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M20" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K20" s="29" t="s">
-        <v>746</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M20" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N20" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O20" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P20" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q20" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R20" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S20" s="29" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N20" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O20" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P20" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q20" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -5496,50 +5013,44 @@
       <c r="E21" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J21" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K21" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M21" s="31" t="s">
+      <c r="F21" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K21" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N21" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O21" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q21" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R21" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S21" s="29" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L21" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N21" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O21" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P21" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q21" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>130</v>
       </c>
@@ -5555,50 +5066,44 @@
       <c r="E22" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>650</v>
-      </c>
-      <c r="J22" s="31" t="s">
-        <v>648</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M22" s="31" t="s">
+      <c r="F22" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J22" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K22" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N22" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q22" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R22" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S22" s="29" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L22" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M22" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N22" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O22" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P22" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q22" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>134</v>
       </c>
@@ -5614,50 +5119,44 @@
       <c r="E23" t="s">
         <v>137</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>650</v>
-      </c>
-      <c r="J23" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K23" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L23" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M23" s="31" t="s">
+      <c r="F23" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J23" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K23" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N23" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O23" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P23" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q23" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R23" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S23" s="29" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L23" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M23" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N23" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O23" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P23" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q23" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>138</v>
       </c>
@@ -5673,50 +5172,44 @@
       <c r="E24" t="s">
         <v>140</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J24" s="31" t="s">
-        <v>648</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M24" s="31" t="s">
+      <c r="F24" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J24" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K24" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N24" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O24" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P24" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q24" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R24" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S24" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L24" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M24" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N24" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O24" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P24" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q24" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -5732,50 +5225,44 @@
       <c r="E25" t="s">
         <v>144</v>
       </c>
-      <c r="F25" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I25" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J25" s="31" t="s">
-        <v>652</v>
-      </c>
-      <c r="K25" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L25" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M25" s="31" t="s">
+      <c r="F25" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K25" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N25" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O25" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P25" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q25" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R25" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S25" s="29" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L25" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M25" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N25" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O25" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P25" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q25" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>145</v>
       </c>
@@ -5791,50 +5278,44 @@
       <c r="E26" t="s">
         <v>128</v>
       </c>
-      <c r="F26" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I26" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="J26" s="31" t="s">
-        <v>654</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M26" s="31" t="s">
+      <c r="F26" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J26" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K26" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N26" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="O26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q26" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R26" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S26" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M26" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="N26" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O26" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P26" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q26" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>148</v>
       </c>
@@ -5850,50 +5331,44 @@
       <c r="E27" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I27" s="29" t="s">
-        <v>654</v>
-      </c>
-      <c r="J27" s="31" t="s">
+      <c r="F27" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J27" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L27" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M27" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="N27" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K27" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L27" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="M27" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N27" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="O27" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P27" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q27" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R27" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S27" s="29" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O27" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P27" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q27" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>494</v>
       </c>
@@ -5909,50 +5384,44 @@
       <c r="E28" t="s">
         <v>570</v>
       </c>
-      <c r="F28" s="28" t="s">
-        <v>732</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I28" s="29" t="s">
-        <v>657</v>
-      </c>
-      <c r="J28" s="31" t="s">
+      <c r="F28" s="31" t="s">
         <v>629</v>
       </c>
-      <c r="K28" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L28" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M28" s="31" t="s">
+      <c r="G28" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J28" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K28" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N28" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O28" s="29" t="s">
-        <v>787</v>
-      </c>
-      <c r="P28" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q28" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R28" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S28" s="29" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M28" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O28" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P28" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q28" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>154</v>
       </c>
@@ -5968,50 +5437,44 @@
       <c r="E29" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="F29" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I29" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J29" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K29" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L29" s="29" t="s">
-        <v>761</v>
-      </c>
-      <c r="M29" s="31" t="s">
+      <c r="F29" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K29" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N29" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O29" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P29" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q29" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R29" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S29" s="29" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M29" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N29" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O29" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P29" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q29" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>189</v>
       </c>
@@ -6027,50 +5490,44 @@
       <c r="E30" t="s">
         <v>192</v>
       </c>
-      <c r="F30" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G30" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I30" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J30" s="31" t="s">
+      <c r="F30" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J30" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K30" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L30" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M30" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K30" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>761</v>
-      </c>
-      <c r="M30" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N30" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O30" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P30" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q30" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R30" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S30" s="29" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N30" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P30" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q30" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>572</v>
       </c>
@@ -6086,50 +5543,44 @@
       <c r="E31" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G31" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H31" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J31" s="31" t="s">
+      <c r="F31" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J31" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K31" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L31" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M31" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N31" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K31" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L31" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M31" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N31" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O31" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P31" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q31" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R31" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S31" s="29" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O31" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P31" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q31" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>574</v>
       </c>
@@ -6145,50 +5596,44 @@
       <c r="E32" t="s">
         <v>577</v>
       </c>
-      <c r="F32" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>724</v>
-      </c>
-      <c r="J32" s="31" t="s">
+      <c r="F32" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J32" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K32" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L32" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M32" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K32" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>767</v>
-      </c>
-      <c r="M32" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N32" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O32" s="29" t="s">
-        <v>788</v>
-      </c>
-      <c r="P32" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q32" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R32" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S32" s="29" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N32" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O32" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P32" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q32" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>264</v>
       </c>
@@ -6204,50 +5649,44 @@
       <c r="E33" t="s">
         <v>600</v>
       </c>
-      <c r="F33" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>725</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>726</v>
-      </c>
-      <c r="J33" s="31" t="s">
-        <v>663</v>
-      </c>
-      <c r="K33" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L33" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M33" s="31" t="s">
+      <c r="F33" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K33" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N33" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O33" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P33" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q33" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R33" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S33" s="29" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L33" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M33" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N33" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O33" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P33" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q33" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>532</v>
       </c>
@@ -6263,50 +5702,44 @@
       <c r="E34" t="s">
         <v>534</v>
       </c>
-      <c r="F34" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G34" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>727</v>
-      </c>
-      <c r="I34" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J34" s="31" t="s">
+      <c r="F34" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J34" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K34" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L34" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M34" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N34" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O34" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P34" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q34" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="K34" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L34" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M34" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N34" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O34" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P34" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q34" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R34" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S34" s="29" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>279</v>
       </c>
@@ -6322,50 +5755,44 @@
       <c r="E35" t="s">
         <v>282</v>
       </c>
-      <c r="F35" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J35" s="31" t="s">
+      <c r="F35" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J35" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K35" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L35" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M35" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K35" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L35" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M35" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N35" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O35" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P35" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q35" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R35" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S35" s="29" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N35" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O35" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P35" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q35" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -6381,50 +5808,44 @@
       <c r="E36" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="28" t="s">
-        <v>733</v>
-      </c>
-      <c r="G36" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J36" s="31" t="s">
+      <c r="F36" s="31" t="s">
         <v>629</v>
       </c>
-      <c r="K36" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L36" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M36" s="31" t="s">
+      <c r="G36" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J36" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K36" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N36" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O36" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P36" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q36" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R36" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S36" s="29" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L36" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M36" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="N36" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="O36" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P36" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q36" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>286</v>
       </c>
@@ -6440,50 +5861,44 @@
       <c r="E37" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G37" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J37" s="31" t="s">
+      <c r="F37" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J37" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L37" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M37" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N37" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K37" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L37" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M37" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N37" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O37" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P37" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q37" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R37" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="S37" s="29" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="O37" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P37" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q37" s="28" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>289</v>
       </c>
@@ -6499,50 +5914,44 @@
       <c r="E38" t="s">
         <v>292</v>
       </c>
-      <c r="F38" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G38" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J38" s="31" t="s">
+      <c r="F38" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K38" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L38" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M38" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K38" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L38" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M38" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N38" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O38" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P38" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q38" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R38" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S38" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N38" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O38" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P38" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q38" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>293</v>
       </c>
@@ -6558,50 +5967,44 @@
       <c r="E39" t="s">
         <v>296</v>
       </c>
-      <c r="F39" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G39" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I39" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J39" s="31" t="s">
+      <c r="F39" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K39" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L39" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M39" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K39" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L39" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M39" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N39" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O39" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P39" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q39" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R39" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S39" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N39" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O39" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P39" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q39" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>298</v>
       </c>
@@ -6617,50 +6020,44 @@
       <c r="E40" t="s">
         <v>602</v>
       </c>
-      <c r="F40" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G40" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I40" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J40" s="31" t="s">
+      <c r="F40" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J40" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K40" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L40" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M40" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K40" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L40" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M40" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N40" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O40" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P40" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q40" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R40" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S40" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N40" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O40" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P40" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q40" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>300</v>
       </c>
@@ -6676,50 +6073,44 @@
       <c r="E41" t="s">
         <v>125</v>
       </c>
-      <c r="F41" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G41" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="H41" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J41" s="31" t="s">
+      <c r="F41" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J41" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K41" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L41" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M41" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K41" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L41" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M41" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N41" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O41" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P41" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q41" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R41" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S41" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N41" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O41" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P41" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q41" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>588</v>
       </c>
@@ -6735,50 +6126,44 @@
       <c r="E42" t="s">
         <v>101</v>
       </c>
-      <c r="F42" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G42" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H42" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I42" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J42" s="31" t="s">
+      <c r="F42" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J42" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K42" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L42" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M42" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K42" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L42" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M42" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N42" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O42" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P42" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q42" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R42" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S42" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N42" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O42" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P42" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q42" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>305</v>
       </c>
@@ -6794,50 +6179,44 @@
       <c r="E43" t="s">
         <v>308</v>
       </c>
-      <c r="F43" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G43" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I43" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J43" s="31" t="s">
+      <c r="F43" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K43" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L43" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M43" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K43" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L43" s="29" t="s">
-        <v>752</v>
-      </c>
-      <c r="M43" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N43" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O43" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P43" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q43" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R43" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S43" s="29" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N43" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O43" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P43" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q43" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>309</v>
       </c>
@@ -6853,50 +6232,44 @@
       <c r="E44" t="s">
         <v>312</v>
       </c>
-      <c r="F44" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G44" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I44" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J44" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K44" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L44" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M44" s="31" t="s">
+      <c r="F44" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K44" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N44" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O44" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P44" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q44" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R44" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S44" s="29" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L44" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M44" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N44" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O44" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P44" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q44" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>313</v>
       </c>
@@ -6912,50 +6285,44 @@
       <c r="E45" t="s">
         <v>296</v>
       </c>
-      <c r="F45" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="J45" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K45" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L45" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M45" s="31" t="s">
+      <c r="F45" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H45" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J45" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K45" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N45" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O45" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P45" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q45" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R45" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S45" s="29" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L45" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M45" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N45" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O45" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P45" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q45" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="149.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>316</v>
       </c>
@@ -6971,50 +6338,44 @@
       <c r="E46" t="s">
         <v>319</v>
       </c>
-      <c r="F46" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G46" s="29" t="s">
-        <v>728</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J46" s="31" t="s">
+      <c r="F46" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K46" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L46" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M46" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K46" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L46" s="29" t="s">
-        <v>758</v>
-      </c>
-      <c r="M46" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N46" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O46" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P46" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q46" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R46" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S46" s="29" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N46" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O46" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P46" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q46" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>320</v>
       </c>
@@ -7030,50 +6391,44 @@
       <c r="E47" t="s">
         <v>323</v>
       </c>
-      <c r="F47" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G47" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H47" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I47" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J47" s="31" t="s">
+      <c r="F47" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J47" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K47" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L47" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M47" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K47" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L47" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M47" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N47" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O47" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P47" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q47" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R47" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S47" s="29" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N47" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O47" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P47" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q47" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>324</v>
       </c>
@@ -7089,50 +6444,44 @@
       <c r="E48" t="s">
         <v>327</v>
       </c>
-      <c r="F48" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G48" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J48" s="31" t="s">
+      <c r="F48" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L48" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M48" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K48" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L48" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M48" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N48" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O48" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P48" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q48" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R48" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S48" s="29" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N48" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O48" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P48" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q48" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>329</v>
       </c>
@@ -7148,50 +6497,44 @@
       <c r="E49" t="s">
         <v>323</v>
       </c>
-      <c r="F49" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G49" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J49" s="31" t="s">
+      <c r="F49" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K49" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L49" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M49" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K49" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L49" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M49" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N49" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O49" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P49" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q49" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R49" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S49" s="29" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O49" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P49" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q49" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>331</v>
       </c>
@@ -7207,50 +6550,44 @@
       <c r="E50" t="s">
         <v>334</v>
       </c>
-      <c r="F50" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G50" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I50" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J50" s="31" t="s">
+      <c r="F50" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K50" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L50" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M50" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K50" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L50" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M50" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N50" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O50" s="29" t="s">
-        <v>789</v>
-      </c>
-      <c r="P50" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q50" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R50" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S50" s="29" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N50" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O50" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P50" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q50" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>343</v>
       </c>
@@ -7266,50 +6603,44 @@
       <c r="E51" t="s">
         <v>128</v>
       </c>
-      <c r="F51" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G51" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J51" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K51" s="29" t="s">
-        <v>748</v>
-      </c>
-      <c r="L51" s="29" t="s">
-        <v>768</v>
-      </c>
-      <c r="M51" s="31" t="s">
+      <c r="F51" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J51" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K51" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N51" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O51" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P51" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q51" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R51" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S51" s="29" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L51" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M51" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N51" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O51" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P51" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q51" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>346</v>
       </c>
@@ -7325,50 +6656,44 @@
       <c r="E52" t="s">
         <v>157</v>
       </c>
-      <c r="F52" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G52" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I52" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J52" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K52" s="29" t="s">
-        <v>748</v>
-      </c>
-      <c r="L52" s="29" t="s">
-        <v>768</v>
-      </c>
-      <c r="M52" s="31" t="s">
+      <c r="F52" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G52" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J52" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K52" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N52" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O52" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P52" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q52" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R52" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S52" s="29" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L52" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M52" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N52" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O52" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P52" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q52" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>349</v>
       </c>
@@ -7384,50 +6709,44 @@
       <c r="E53" t="s">
         <v>352</v>
       </c>
-      <c r="F53" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G53" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J53" s="31" t="s">
+      <c r="F53" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J53" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K53" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L53" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M53" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K53" s="29" t="s">
-        <v>749</v>
-      </c>
-      <c r="L53" s="29" t="s">
-        <v>769</v>
-      </c>
-      <c r="M53" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N53" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O53" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P53" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q53" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R53" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S53" s="29" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N53" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O53" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P53" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q53" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>354</v>
       </c>
@@ -7443,50 +6762,44 @@
       <c r="E54" t="s">
         <v>357</v>
       </c>
-      <c r="F54" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G54" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I54" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J54" s="31" t="s">
+      <c r="F54" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G54" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H54" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J54" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K54" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L54" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M54" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N54" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O54" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P54" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q54" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="K54" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L54" s="29" t="s">
-        <v>770</v>
-      </c>
-      <c r="M54" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N54" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O54" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P54" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q54" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R54" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S54" s="29" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:17" ht="120.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>619</v>
       </c>
@@ -7502,50 +6815,44 @@
       <c r="E55" t="s">
         <v>529</v>
       </c>
-      <c r="F55" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G55" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I55" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J55" s="31" t="s">
+      <c r="F55" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J55" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K55" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L55" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M55" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K55" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L55" s="29" t="s">
-        <v>758</v>
-      </c>
-      <c r="M55" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N55" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O55" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P55" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q55" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R55" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="S55" s="29" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N55" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O55" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P55" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q55" s="28" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>620</v>
       </c>
@@ -7561,50 +6868,44 @@
       <c r="E56" t="s">
         <v>128</v>
       </c>
-      <c r="F56" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G56" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H56" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I56" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J56" s="31" t="s">
+      <c r="F56" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G56" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K56" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L56" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M56" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N56" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O56" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P56" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q56" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="K56" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L56" s="29" t="s">
-        <v>758</v>
-      </c>
-      <c r="M56" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N56" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O56" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P56" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q56" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R56" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S56" s="29" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:17" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>390</v>
       </c>
@@ -7620,50 +6921,44 @@
       <c r="E57" t="s">
         <v>393</v>
       </c>
-      <c r="F57" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G57" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H57" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I57" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J57" s="31" t="s">
+      <c r="F57" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K57" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L57" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M57" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K57" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L57" s="29" t="s">
-        <v>758</v>
-      </c>
-      <c r="M57" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N57" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O57" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P57" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q57" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R57" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S57" s="29" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N57" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O57" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P57" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q57" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>359</v>
       </c>
@@ -7679,50 +6974,44 @@
       <c r="E58" t="s">
         <v>362</v>
       </c>
-      <c r="F58" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G58" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H58" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I58" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J58" s="31" t="s">
+      <c r="F58" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G58" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H58" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J58" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K58" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L58" s="35" t="s">
+        <v>628</v>
+      </c>
+      <c r="M58" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K58" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="L58" s="29" t="s">
-        <v>750</v>
-      </c>
-      <c r="M58" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N58" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O58" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P58" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q58" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R58" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S58" s="29" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N58" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O58" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P58" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q58" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>363</v>
       </c>
@@ -7738,50 +7027,44 @@
       <c r="E59" t="s">
         <v>365</v>
       </c>
-      <c r="F59" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G59" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H59" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I59" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J59" s="31" t="s">
+      <c r="F59" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G59" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H59" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I59" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J59" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K59" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L59" s="35" t="s">
+        <v>628</v>
+      </c>
+      <c r="M59" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K59" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L59" s="29" t="s">
-        <v>750</v>
-      </c>
-      <c r="M59" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N59" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O59" s="29" t="s">
-        <v>788</v>
-      </c>
-      <c r="P59" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q59" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R59" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="S59" s="29" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N59" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O59" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P59" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q59" s="28" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>366</v>
       </c>
@@ -7797,50 +7080,44 @@
       <c r="E60" t="s">
         <v>365</v>
       </c>
-      <c r="F60" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G60" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="H60" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I60" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J60" s="31" t="s">
+      <c r="F60" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="H60" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J60" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="K60" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L60" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M60" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K60" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="L60" s="29" t="s">
-        <v>771</v>
-      </c>
-      <c r="M60" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N60" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O60" s="29" t="s">
-        <v>788</v>
-      </c>
-      <c r="P60" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q60" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R60" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S60" s="29" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N60" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O60" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P60" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q60" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>595</v>
       </c>
@@ -7856,50 +7133,44 @@
       <c r="E61" t="s">
         <v>101</v>
       </c>
-      <c r="F61" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G61" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H61" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I61" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J61" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K61" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L61" s="29" t="s">
-        <v>771</v>
-      </c>
-      <c r="M61" s="31" t="s">
+      <c r="F61" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K61" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N61" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O61" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P61" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q61" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R61" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S61" s="29" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L61" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M61" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N61" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O61" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P61" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q61" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>371</v>
       </c>
@@ -7915,50 +7186,44 @@
       <c r="E62" t="s">
         <v>101</v>
       </c>
-      <c r="F62" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G62" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H62" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I62" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J62" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K62" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L62" s="29" t="s">
-        <v>771</v>
-      </c>
-      <c r="M62" s="31" t="s">
+      <c r="F62" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J62" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K62" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N62" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O62" s="29" t="s">
-        <v>789</v>
-      </c>
-      <c r="P62" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q62" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R62" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S62" s="29" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L62" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M62" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N62" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O62" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P62" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q62" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>373</v>
       </c>
@@ -7974,50 +7239,44 @@
       <c r="E63" t="s">
         <v>376</v>
       </c>
-      <c r="F63" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G63" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H63" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I63" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J63" s="31" t="s">
+      <c r="F63" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J63" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K63" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L63" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M63" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K63" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L63" s="29" t="s">
-        <v>751</v>
-      </c>
-      <c r="M63" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N63" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O63" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P63" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q63" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R63" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S63" s="29" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N63" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O63" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P63" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q63" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>548</v>
       </c>
@@ -8033,50 +7292,44 @@
       <c r="E64" t="s">
         <v>589</v>
       </c>
-      <c r="F64" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G64" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H64" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I64" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J64" s="31" t="s">
+      <c r="F64" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G64" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H64" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I64" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J64" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K64" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L64" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M64" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N64" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K64" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L64" s="29" t="s">
-        <v>772</v>
-      </c>
-      <c r="M64" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N64" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O64" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P64" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q64" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R64" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="S64" s="29" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="O64" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P64" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q64" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>489</v>
       </c>
@@ -8092,50 +7345,44 @@
       <c r="E65" t="s">
         <v>128</v>
       </c>
-      <c r="F65" s="28" t="s">
-        <v>667</v>
-      </c>
-      <c r="G65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J65" s="31" t="s">
+      <c r="F65" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G65" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H65" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I65" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J65" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K65" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L65" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M65" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L65" s="29" t="s">
-        <v>773</v>
-      </c>
-      <c r="M65" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N65" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O65" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q65" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R65" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S65" s="29" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N65" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O65" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P65" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q65" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>397</v>
       </c>
@@ -8151,50 +7398,44 @@
       <c r="E66" t="s">
         <v>400</v>
       </c>
-      <c r="F66" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H66" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I66" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J66" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K66" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L66" s="29" t="s">
-        <v>771</v>
-      </c>
-      <c r="M66" s="31" t="s">
+      <c r="F66" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G66" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H66" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I66" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J66" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K66" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N66" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O66" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P66" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q66" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R66" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="S66" s="29" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L66" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M66" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N66" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O66" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P66" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q66" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="81.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>394</v>
       </c>
@@ -8210,50 +7451,44 @@
       <c r="E67" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="28" t="s">
-        <v>667</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H67" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I67" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J67" s="31" t="s">
+      <c r="F67" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G67" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H67" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I67" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J67" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K67" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L67" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M67" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K67" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L67" s="29" t="s">
-        <v>774</v>
-      </c>
-      <c r="M67" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N67" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O67" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P67" s="29" t="s">
-        <v>670</v>
-      </c>
-      <c r="Q67" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R67" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S67" s="29" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N67" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O67" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P67" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q67" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>377</v>
       </c>
@@ -8269,50 +7504,44 @@
       <c r="E68" t="s">
         <v>380</v>
       </c>
-      <c r="F68" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G68" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H68" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I68" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J68" s="31" t="s">
+      <c r="F68" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H68" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I68" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J68" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K68" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L68" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M68" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K68" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L68" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="M68" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N68" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O68" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P68" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q68" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R68" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S68" s="29" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N68" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O68" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P68" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q68" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>381</v>
       </c>
@@ -8328,50 +7557,44 @@
       <c r="E69" t="s">
         <v>101</v>
       </c>
-      <c r="F69" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H69" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I69" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J69" s="31" t="s">
+      <c r="F69" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G69" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H69" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I69" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J69" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K69" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L69" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M69" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K69" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L69" s="29" t="s">
-        <v>776</v>
-      </c>
-      <c r="M69" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N69" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O69" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P69" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q69" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R69" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="S69" s="29" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N69" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O69" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P69" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q69" s="28" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>508</v>
       </c>
@@ -8387,50 +7610,44 @@
       <c r="E70" t="s">
         <v>423</v>
       </c>
-      <c r="F70" s="28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G70" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H70" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I70" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J70" s="31" t="s">
+      <c r="F70" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G70" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H70" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I70" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J70" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K70" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L70" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M70" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N70" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K70" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L70" s="29" t="s">
-        <v>776</v>
-      </c>
-      <c r="M70" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N70" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O70" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="P70" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q70" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="R70" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S70" s="29" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O70" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="P70" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q70" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19" t="s">
         <v>384</v>
       </c>
@@ -8446,50 +7663,44 @@
       <c r="E71" t="s">
         <v>387</v>
       </c>
-      <c r="F71" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G71" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H71" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I71" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J71" s="31" t="s">
+      <c r="F71" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G71" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H71" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I71" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J71" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K71" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L71" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M71" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K71" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L71" s="29" t="s">
-        <v>762</v>
-      </c>
-      <c r="M71" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N71" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O71" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P71" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q71" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="R71" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S71" s="29" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O71" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P71" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q71" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>596</v>
       </c>
@@ -8505,50 +7716,44 @@
       <c r="E72" t="s">
         <v>108</v>
       </c>
-      <c r="F72" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G72" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H72" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="I72" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J72" s="31" t="s">
-        <v>629</v>
-      </c>
-      <c r="K72" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L72" s="29" t="s">
-        <v>763</v>
-      </c>
-      <c r="M72" s="31" t="s">
+      <c r="F72" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G72" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H72" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="I72" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J72" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K72" s="30" t="s">
         <v>624</v>
       </c>
-      <c r="N72" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O72" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P72" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q72" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R72" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="S72" s="29" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L72" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M72" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N72" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O72" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P72" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q72" s="28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>432</v>
       </c>
@@ -8564,50 +7769,44 @@
       <c r="E73" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G73" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H73" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I73" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J73" s="31" t="s">
+      <c r="F73" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G73" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H73" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I73" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="J73" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K73" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L73" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M73" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K73" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L73" s="29" t="s">
-        <v>777</v>
-      </c>
-      <c r="M73" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N73" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O73" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P73" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q73" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R73" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S73" s="29" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N73" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O73" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P73" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q73" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>483</v>
       </c>
@@ -8623,111 +7822,103 @@
       <c r="E74" t="s">
         <v>482</v>
       </c>
-      <c r="F74" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J74" s="31" t="s">
+      <c r="F74" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G74" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H74" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J74" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K74" s="30" t="s">
+        <v>624</v>
+      </c>
+      <c r="L74" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M74" s="33" t="s">
         <v>629</v>
       </c>
-      <c r="K74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L74" s="29" t="s">
-        <v>777</v>
-      </c>
-      <c r="M74" s="31" t="s">
-        <v>624</v>
-      </c>
-      <c r="N74" s="29" t="s">
-        <v>702</v>
-      </c>
-      <c r="O74" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q74" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R74" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S74" s="29" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="N74" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O74" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P74" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q74" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>812</v>
+        <v>653</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>794</v>
+        <v>636</v>
       </c>
       <c r="C75" t="s">
-        <v>800</v>
+        <v>642</v>
       </c>
       <c r="D75">
         <v>2025</v>
       </c>
       <c r="E75" t="s">
-        <v>806</v>
-      </c>
-      <c r="F75" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G75" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H75" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I75" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J75" s="31"/>
-      <c r="K75" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L75" s="29" t="s">
-        <v>813</v>
-      </c>
-      <c r="M75" s="31"/>
-      <c r="N75" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O75" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P75" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q75" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R75" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S75" s="29"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+        <v>648</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G75" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H75" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I75" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J75" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K75" s="30"/>
+      <c r="L75" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M75" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N75" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O75" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P75" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q75" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="14.3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>811</v>
+        <v>652</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>795</v>
+        <v>637</v>
       </c>
       <c r="C76" t="s">
-        <v>801</v>
+        <v>643</v>
       </c>
       <c r="D76">
         <v>2025</v>
@@ -8735,211 +7926,203 @@
       <c r="E76" t="s">
         <v>157</v>
       </c>
-      <c r="F76" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G76" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H76" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="I76" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J76" s="31"/>
-      <c r="K76" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L76" s="29" t="s">
-        <v>813</v>
-      </c>
-      <c r="M76" s="31"/>
-      <c r="N76" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O76" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="P76" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q76" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R76" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S76" s="29"/>
-    </row>
-    <row r="77" spans="1:19" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F76" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G76" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H76" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="I76" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J76" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K76" s="30"/>
+      <c r="L76" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M76" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N76" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="O76" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P76" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q76" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>790</v>
+        <v>632</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>796</v>
+        <v>638</v>
       </c>
       <c r="C77" t="s">
-        <v>802</v>
+        <v>644</v>
       </c>
       <c r="D77">
         <v>2025</v>
       </c>
       <c r="E77" t="s">
-        <v>807</v>
-      </c>
-      <c r="F77" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G77" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H77" s="29" t="s">
-        <v>810</v>
-      </c>
-      <c r="I77" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J77" s="31"/>
-      <c r="K77" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L77" s="29" t="s">
-        <v>813</v>
-      </c>
-      <c r="M77" s="31"/>
-      <c r="N77" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O77" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P77" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q77" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="R77" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S77" s="29"/>
-    </row>
-    <row r="78" spans="1:19" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>649</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G77" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H77" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I77" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J77" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K77" s="30"/>
+      <c r="L77" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M77" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N77" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O77" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P77" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q77" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>791</v>
+        <v>633</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>797</v>
+        <v>639</v>
       </c>
       <c r="C78" t="s">
-        <v>803</v>
+        <v>645</v>
       </c>
       <c r="D78">
         <v>2023</v>
       </c>
       <c r="E78" t="s">
-        <v>808</v>
-      </c>
-      <c r="F78" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G78" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H78" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I78" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J78" s="31"/>
-      <c r="K78" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L78" s="29" t="s">
-        <v>814</v>
-      </c>
-      <c r="M78" s="31"/>
-      <c r="N78" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O78" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P78" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="Q78" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R78" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S78" s="29"/>
-    </row>
-    <row r="79" spans="1:19" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H78" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I78" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J78" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K78" s="30"/>
+      <c r="L78" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M78" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N78" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O78" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="P78" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q78" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>793</v>
+        <v>635</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>799</v>
+        <v>641</v>
       </c>
       <c r="C79" t="s">
-        <v>805</v>
+        <v>647</v>
       </c>
       <c r="D79">
         <v>2025</v>
       </c>
       <c r="E79" t="s">
-        <v>809</v>
-      </c>
-      <c r="F79" s="28" t="s">
-        <v>625</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H79" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I79" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J79" s="31"/>
-      <c r="K79" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="L79" s="29" t="s">
-        <v>815</v>
-      </c>
-      <c r="M79" s="31"/>
-      <c r="N79" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O79" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="P79" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q79" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="R79" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S79" s="29"/>
-    </row>
-    <row r="80" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>651</v>
+      </c>
+      <c r="F79" s="31" t="s">
+        <v>625</v>
+      </c>
+      <c r="G79" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H79" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I79" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J79" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="K79" s="30"/>
+      <c r="L79" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="M79" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N79" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="O79" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="P79" s="28" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q79" s="28" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="14.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>792</v>
+        <v>634</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>798</v>
+        <v>640</v>
       </c>
       <c r="C80" t="s">
-        <v>804</v>
+        <v>646</v>
       </c>
       <c r="D80">
         <v>2025</v>
@@ -8947,50 +8130,47 @@
       <c r="E80" t="s">
         <v>101</v>
       </c>
-      <c r="F80" s="28" t="s">
-        <v>626</v>
-      </c>
-      <c r="G80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="H80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="I80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="J80" s="31"/>
-      <c r="K80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="L80" s="29" t="s">
-        <v>771</v>
-      </c>
-      <c r="M80" s="31"/>
-      <c r="N80" s="29" t="s">
-        <v>701</v>
-      </c>
-      <c r="O80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="P80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="Q80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="R80" s="29" t="s">
-        <v>626</v>
-      </c>
-      <c r="S80" s="29"/>
+      <c r="F80" s="31" t="s">
+        <v>626</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="H80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="I80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="J80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K80" s="30"/>
+      <c r="L80" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="M80" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="N80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="O80" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="P80" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q80" s="28" t="s">
+        <v>626</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8998,9 +8178,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76454F8C-CCDD-40C2-96B3-0FCB86438C20}">
   <dimension ref="A1:BH30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:52" s="6" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" s="6" customFormat="1" ht="114.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -9146,7 +8326,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:52" s="1" customFormat="1" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" s="1" customFormat="1" ht="67.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
@@ -9277,7 +8457,7 @@
       </c>
       <c r="AU2" s="4"/>
     </row>
-    <row r="3" spans="1:52" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" ht="97.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>44</v>
       </c>
@@ -9428,7 +8608,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="102.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" ht="102.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>44</v>
       </c>
@@ -9558,7 +8738,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" ht="114.15" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>44</v>
       </c>
@@ -9691,7 +8871,7 @@
       </c>
       <c r="AU5" s="4"/>
     </row>
-    <row r="6" spans="1:52" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" ht="185.45" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>44</v>
       </c>
@@ -9833,7 +9013,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" ht="370.9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>44</v>
       </c>
@@ -9970,7 +9150,7 @@
       </c>
       <c r="AU7" s="4"/>
     </row>
-    <row r="8" spans="1:52" ht="134.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" ht="134.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>487</v>
       </c>
@@ -10094,7 +9274,7 @@
       </c>
       <c r="AU8" s="4"/>
     </row>
-    <row r="9" spans="1:52" ht="193.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" ht="193.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>44</v>
       </c>
@@ -10238,7 +9418,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>493</v>
       </c>
@@ -10246,7 +9426,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" ht="85.6" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>514</v>
       </c>
@@ -10257,7 +9437,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="144" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" ht="142.65" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>499</v>
       </c>
@@ -10265,7 +9445,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" ht="142.65" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>501</v>
       </c>
@@ -10276,7 +9456,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="144" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" ht="142.65" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>504</v>
       </c>
@@ -10290,7 +9470,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" ht="99.85" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>514</v>
       </c>
@@ -10304,7 +9484,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" ht="214" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>518</v>
       </c>
@@ -10321,7 +9501,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="17" spans="1:60" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:60" ht="199.7" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>539</v>
       </c>
@@ -10335,7 +9515,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="18" spans="1:60" ht="144" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:60" ht="142.65" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>133</v>
       </c>
@@ -10371,7 +9551,7 @@
       <c r="AR18" s="3"/>
       <c r="AS18" s="4"/>
     </row>
-    <row r="19" spans="1:60" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:60" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>133</v>
       </c>
@@ -10411,7 +9591,7 @@
       <c r="AR19" s="3"/>
       <c r="AS19" s="4"/>
     </row>
-    <row r="20" spans="1:60" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:60" ht="128.4" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>427</v>
       </c>
@@ -10451,7 +9631,7 @@
       <c r="AR20" s="3"/>
       <c r="AS20" s="4"/>
     </row>
-    <row r="21" spans="1:60" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:60" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>133</v>
       </c>
@@ -10491,7 +9671,7 @@
       <c r="AR21" s="3"/>
       <c r="AS21" s="4"/>
     </row>
-    <row r="22" spans="1:60" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:60" ht="171.2" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>544</v>
       </c>
@@ -10508,7 +9688,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="23" spans="1:60" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:60" ht="171.2" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
         <v>552</v>
       </c>
@@ -10516,7 +9696,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="24" spans="1:60" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:60" ht="228.25" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>133</v>
       </c>
@@ -10563,7 +9743,7 @@
       <c r="AJ24" s="2"/>
       <c r="AS24" s="4"/>
     </row>
-    <row r="25" spans="1:60" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:60" ht="99.85" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" t="s">
         <v>563</v>
@@ -10606,7 +9786,7 @@
       <c r="AR25" s="3"/>
       <c r="AS25" s="4"/>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>563</v>
       </c>
@@ -10620,7 +9800,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="1:60" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:60" ht="313.85000000000002" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>44</v>
       </c>
@@ -10752,7 +9932,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:60" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:60" ht="285.3" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>133</v>
       </c>
@@ -10802,7 +9982,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:60" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:60" ht="199.7" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>44</v>
       </c>
@@ -10940,7 +10120,7 @@
       <c r="AY29" s="22"/>
       <c r="AZ29" s="22"/>
     </row>
-    <row r="30" spans="1:60" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:60" ht="128.4" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>618</v>
       </c>
@@ -11122,7 +10302,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93B0FB6D-30AC-4478-8817-8144130A4A1E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11131,9 +10311,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB3AB17-A34E-42CA-BBA8-CF8599AC2147}">
   <dimension ref="A1:AY3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:51" s="6" customFormat="1" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" s="6" customFormat="1" ht="114.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -11279,7 +10459,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" ht="199.7" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>581</v>
       </c>
@@ -11336,7 +10516,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:51" ht="360" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:51" ht="356.6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>586</v>
       </c>
@@ -11407,11 +10587,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="e462866a-86d3-44af-9496-8f6279a8194a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11636,27 +10817,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e462866a-86d3-44af-9496-8f6279a8194a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7834F97-8AFB-4D16-B264-B83FC8D5A53A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FECF07E-23D0-4C40-85F2-7A1AF772DB7C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="e462866a-86d3-44af-9496-8f6279a8194a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e821a6d3-8b51-427c-89dc-11a9f9dfeeff"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11681,9 +10852,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FECF07E-23D0-4C40-85F2-7A1AF772DB7C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7834F97-8AFB-4D16-B264-B83FC8D5A53A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="e462866a-86d3-44af-9496-8f6279a8194a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e821a6d3-8b51-427c-89dc-11a9f9dfeeff"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>